--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B258C9E9-01CA-4FF6-8B27-D6A1ED0DE189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6328E1D-3BFB-45EC-AC3D-63888547C63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 19-12-2025'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 29-01-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6328E1D-3BFB-45EC-AC3D-63888547C63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6880CDE8-6757-4A0C-9709-7C9EE01103F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 29-01-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-02-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6880CDE8-6757-4A0C-9709-7C9EE01103F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7002E0AA-F35E-431F-AFF9-64A9BB9D9EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-02-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 20-02-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7002E0AA-F35E-431F-AFF9-64A9BB9D9EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF870113-D6F3-4008-855E-70F8884144D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 20-02-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 04-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF870113-D6F3-4008-855E-70F8884144D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6364CDB3-45D1-4E98-B530-7772EA96EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 04-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6364CDB3-45D1-4E98-B530-7772EA96EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60D5E74-81FC-47CE-B924-F407A430B443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60D5E74-81FC-47CE-B924-F407A430B443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471C33BD-19AE-4A38-A7FB-74FDCB8A02E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471C33BD-19AE-4A38-A7FB-74FDCB8A02E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61140097-D0A8-4926-85FC-28DC0469DB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61140097-D0A8-4926-85FC-28DC0469DB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE15243-6290-458B-A53C-6F046511BFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE15243-6290-458B-A53C-6F046511BFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EBE197-946F-4A8B-892B-D00620111D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 11-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EBE197-946F-4A8B-892B-D00620111D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFF10F-BF74-459C-91A3-7C33F2F57AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFF10F-BF74-459C-91A3-7C33F2F57AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CE6930-12B8-4F1E-BC6F-2DDCF122944A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 11-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 20-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CE6930-12B8-4F1E-BC6F-2DDCF122944A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF79F1E8-7A99-40F8-A60C-AB82D7E548BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 20-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 25-03-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF79F1E8-7A99-40F8-A60C-AB82D7E548BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E79C70-A63E-4CEF-B9B8-0546DA3C4FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 25-03-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 08-04-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E79C70-A63E-4CEF-B9B8-0546DA3C4FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF06EF06-2A2C-4D00-9093-C59DA068E893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 08-04-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 10-04-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF06EF06-2A2C-4D00-9093-C59DA068E893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB53BECE-C773-4A24-9EC0-6284F49C497D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB53BECE-C773-4A24-9EC0-6284F49C497D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C0988A-8A4C-400E-8ACC-943F3A66DA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 10-04-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 14-04-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C0988A-8A4C-400E-8ACC-943F3A66DA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A161433-0FF2-4221-A97D-7ABD12E0154E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 14-04-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 24-04-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A161433-0FF2-4221-A97D-7ABD12E0154E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE73246-B6D2-403B-A8B0-CB36B1053F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE73246-B6D2-403B-A8B0-CB36B1053F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970AB437-03D3-4929-83BB-F1AF0AAB3F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 24-04-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 27-04-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970AB437-03D3-4929-83BB-F1AF0AAB3F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED82514-08C8-4DC7-BF79-22729DB6D7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 27-04-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-05-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED82514-08C8-4DC7-BF79-22729DB6D7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54679003-05F2-4C59-8CA4-B6C6709B26A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-05-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 01-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54679003-05F2-4C59-8CA4-B6C6709B26A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F450AE2-A376-4D31-99EC-B202D1849497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 01-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F450AE2-A376-4D31-99EC-B202D1849497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EBDD9F-ADF7-4C28-A5ED-042286DCD546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EBDD9F-ADF7-4C28-A5ED-042286DCD546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC5D65-6431-469F-B45D-2294C31D83C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 05-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6328E1D-3BFB-45EC-AC3D-63888547C63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED51C6DC-5F17-4406-9FCB-8148F1BA4EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC57466-B47D-4F44-B10E-5AF6FB97F8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501CCD6F-D1CE-4D73-997F-A2E8BC1EC94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501CCD6F-D1CE-4D73-997F-A2E8BC1EC94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C437F90-D4F7-400E-B54A-CF9621002599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C437F90-D4F7-400E-B54A-CF9621002599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA63921-B104-4C75-ACE3-1FFD5F4AFAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 15-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA63921-B104-4C75-ACE3-1FFD5F4AFAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78933E8B-1799-4B85-9EE5-F1B798894407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 15-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78933E8B-1799-4B85-9EE5-F1B798894407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB82B10-ECC3-4F35-B281-2FC906602D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB82B10-ECC3-4F35-B281-2FC906602D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7E326E-A19B-4BE8-8CA2-8FB8ACC1DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78933E8B-1799-4B85-9EE5-F1B798894407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD2D136-3367-4EFD-882F-440FCB019633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD2D136-3367-4EFD-882F-440FCB019633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB1A69D-548D-45AE-A8F9-66179EF521F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 25-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB1A69D-548D-45AE-A8F9-66179EF521F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0EF8D1-B15F-4502-A3FB-0DA93FD230AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 25-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 30-06-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0EF8D1-B15F-4502-A3FB-0DA93FD230AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643E0A80-89D1-4781-B8D9-096FD6696952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643E0A80-89D1-4781-B8D9-096FD6696952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FE87D4-E35D-497B-91AC-EE848EC248D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 30-06-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 01-07-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FE87D4-E35D-497B-91AC-EE848EC248D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86A32B5-62AA-4442-8E6C-7136D7488DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 01-07-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-07-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FE87D4-E35D-497B-91AC-EE848EC248D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D06EEF-2A27-4FAF-89AE-4C7D44DD4BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 01-07-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 03-07-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86A32B5-62AA-4442-8E6C-7136D7488DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794CDC5F-F665-424E-9981-F8AAC7DFD1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-07-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 03-07-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794CDC5F-F665-424E-9981-F8AAC7DFD1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1237611-B7F7-4B7A-8595-BA99182B7AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 03-07-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-07-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1237611-B7F7-4B7A-8595-BA99182B7AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47738117-D7F7-458E-A1D1-AF7BEC68A701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-07-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 19-08-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47738117-D7F7-458E-A1D1-AF7BEC68A701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC52ADE-51B1-4BFD-A697-37E07CFC0114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 19-08-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 21-08-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC52ADE-51B1-4BFD-A697-37E07CFC0114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995F257-10DE-4074-A06C-79C1F5D3F6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 21-08-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 27-08-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995F257-10DE-4074-A06C-79C1F5D3F6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E15D847-610B-48D0-A884-65FE53A8F091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 27-08-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E15D847-610B-48D0-A884-65FE53A8F091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6CDE2E-BE07-4FA2-9510-7A55D81D760E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6CDE2E-BE07-4FA2-9510-7A55D81D760E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019B5DA3-3F90-4A8F-A895-0099A45D1F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019B5DA3-3F90-4A8F-A895-0099A45D1F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3A00BF-8147-4095-8A06-D3694CC40867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 06-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 07-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3A00BF-8147-4095-8A06-D3694CC40867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1F8BA7-809E-4D04-9B77-606C475817A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 07-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1F8BA7-809E-4D04-9B77-606C475817A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11B4DD4-D163-4F57-A61D-9C7DEE0C84CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
